--- a/data/config/project_map.xlsx
+++ b/data/config/project_map.xlsx
@@ -727,11 +727,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1058,15 +1055,15 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
@@ -1074,7 +1071,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>1220153829</v>
       </c>
       <c r="B3" t="s">
@@ -1082,7 +1079,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>1220163947</v>
       </c>
       <c r="B4" t="s">
@@ -1090,7 +1087,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>1220146814</v>
       </c>
       <c r="B5" t="s">
@@ -1098,7 +1095,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>1220139490</v>
       </c>
       <c r="B6" t="s">
@@ -1106,7 +1103,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>1220084903</v>
       </c>
       <c r="B7" t="s">
@@ -1114,7 +1111,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>1220201087</v>
       </c>
       <c r="B8" t="s">
@@ -1122,7 +1119,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>1220143092</v>
       </c>
       <c r="B9" t="s">
@@ -1130,7 +1127,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>1220192505</v>
       </c>
       <c r="B10" t="s">
@@ -1138,7 +1135,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>1220192506</v>
       </c>
       <c r="B11" t="s">
@@ -1146,7 +1143,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>1220148025</v>
       </c>
       <c r="B12" t="s">
@@ -1154,7 +1151,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>1220149217</v>
       </c>
       <c r="B13" t="s">
@@ -1162,7 +1159,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>1220164156</v>
       </c>
       <c r="B14" t="s">
@@ -1170,7 +1167,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>1220153721</v>
       </c>
       <c r="B15" t="s">
@@ -1178,7 +1175,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>1220201088</v>
       </c>
       <c r="B16" t="s">
@@ -1186,7 +1183,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>1220183586</v>
       </c>
       <c r="B17" t="s">
@@ -1194,7 +1191,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>1220200746</v>
       </c>
       <c r="B18" t="s">
@@ -1202,7 +1199,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>1220203257</v>
       </c>
       <c r="B19" t="s">
@@ -1210,7 +1207,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>1220183829</v>
       </c>
       <c r="B20" t="s">
@@ -1218,7 +1215,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="3">
+      <c r="A21" s="2">
         <v>1220187538</v>
       </c>
       <c r="B21" t="s">
@@ -1226,7 +1223,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>1220191204</v>
       </c>
       <c r="B22" t="s">
@@ -1234,7 +1231,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="3">
+      <c r="A23" s="2">
         <v>1220168618</v>
       </c>
       <c r="B23" t="s">
